--- a/Planificacion_Normativa_UMAG.xlsx
+++ b/Planificacion_Normativa_UMAG.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Dependencias" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planificación Hitos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Ejecutivo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisitos Legales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Dependencias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planificación Hitos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Ejecutivo" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +64,31 @@
       <b val="1"/>
       <color rgb="00C0392B"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -149,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -199,6 +225,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,6 +619,1008 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Reglamento</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Fuente Legal</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Requisito Exacto del Estatuto/Ley</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>Contenido Mínimo Obligatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>Funcionamiento CS</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Art. 20 Estatuto</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>«La Universidad definirá a través de reglamentos, y previo acuerdo del CS, las normas sobre el funcionamiento interno de este Consejo, en todo aquello que no esté previsto en el presente Estatuto.»</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Renovación parcial (Art. 12); quórum mínimo 6 (Art. 19); sesiones trimestrales (Art. 20); causales de cesación por inasistencia (Art. 12 inc. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Bienes de Especial Interés</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>Art. 18 g) Estatuto</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>«La declaración de bienes de especial interés institucional se sujetará a la normativa y procedimientos definidos en un reglamento dictado por el Rector con aprobación del CU.»</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Procedimiento de declaración; criterios de clasificación; requisitos para enajenación o gravamen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Elección del Rector</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Art. 22 Estatuto + Ley 19.305</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>«El Rector se elegirá de conformidad con la ley N° 19.305 y lo que establezca el Reglamento de elección del rector.»</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Procedimiento electoral conforme Ley 19.305; derecho a voto de académicos con nombramiento vigente en planta o contrata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Nombramiento CS</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>Art. 12-13 Estatuto</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>El CU nombra 4 integrantes del CS. Art. 13 define representación de la comunidad universitaria.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Procedimiento de nombramiento; 2 académicos altas jerarquías + 1 funcionario + 1 estudiante; inhabilitaciones (Art. 14); fuero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Funcionamiento CU</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Art. 32 Estatuto</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>«Las normas serán establecidas en un reglamento dictado por él mismo, el cual deberá incluir disposiciones que regulen su renovación parcial.»</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Renovación parcial; comisiones permanentes y temporales; representación (académicos ≥ 2/3 del total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Elecciones Generales</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Art. 13, 29, 58, 61, 62, 63 Estatuto</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Múltiples artículos requieren que órganos y cargos se elijan conforme al Reglamento General de Elecciones.</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Elección representantes CS, CU, Consejos de Facultad, Directores de Departamento, Instituto y Centro</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Secretaría General</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Art. 39 Estatuto</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Debe definir las unidades que componen la SG y las responsabilidades de cada una. Incluir Fiscalía Universitaria.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Unidades de SG; funciones de cada una; Fiscalía Universitaria para investigaciones sumarias y sumarios administrativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>General de Facultades</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Art. 57-59, 64 Estatuto</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Art. 64: «Mediante uno o más reglamentos, se regularán las atribuciones, funciones, organización interna, normas de funcionamiento de las estructuras académicas.»</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Organización de Facultades; Consejo de Facultad y sus atribuciones (Art. 59: presupuesto, planes, proyectos); creación/modificación/cierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Gestión Calidad</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Art. 49-53 Estatuto + Ley 20.129</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Art. 53: Atribuciones del Comité: coordinar procesos de calidad y acreditación, constituir comisiones, informar cumplimiento, supervisar tutoría.</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Procesos de acreditación institucional y de carreras; comisiones generales y locales; plan de tutoría (Ley 21.094 Art. 33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Estudios</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Art. 55 Estatuto</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>«Un reglamento establecerá la duración de cada período lectivo, exigencias, requisitos y el sistema de medición de los estudios y otras materias atingentes.»</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Duración períodos lectivos; exigencias y requisitos; sistema de medición; modalidad presencial/distancia; cursos de extensión</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Estructuras Académicas</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Art. 56, 60-64 Estatuto</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Art. 64: Misma base que #8. Art. 60-63 definen Departamentos, Institutos y Centros.</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Departamentos (Art. 60); Institutos (Art. 62); Centros (Art. 63); creación/modificación/cierre de unidades; Director y Consejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Comité Calidad</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Art. 51-52, 54 Estatuto</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Art. 54: «Se regulará organización interna del Comité y Unidad de Aseguramiento: número, designación, duración, requisitos, atribuciones y funcionamiento.» Aprobación: 2/3 del CU.</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Composición (Rector + Vicerrectores mínimo); forma de designación; duración; requisitos; atribuciones; funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Carrera Académica</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Art. 67 Estatuto</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>«La Universidad deberá establecer funciones, plazos, derechos y obligaciones. Contener normas sobre jerarquía, ingreso, permanencia, promoción, remoción, cesación, evaluación y calificación. Metas de docencia, investigación y vinculación acorde PEDI y PEI.»</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Funciones; plazos de nombramiento; derechos/obligaciones; jerarquía; ingreso/permanencia/promoción/remoción/cesación; evaluación; metas; estímulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Carga Académica</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Art. 67 (derivado)</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Derivado de Art. 67 sobre funciones y obligaciones académicas.</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Distribución de carga docente, investigativa y de vinculación; criterios de asignación</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Jerarquía Académica</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Art. 68 Estatuto</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Art. 68: 4 jerarquías (Titular, Asociado, Asistente, Instructor). «Un reglamento regulará composición y funcionamiento de la comisión de nombramiento o promoción, además de los criterios.»</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Comisión de nombramiento/promoción; criterios por jerarquía; evaluación académica obligatoria para nuevos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Promoción Académico</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>En Proceso</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Art. 68 Estatuto</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>«Un reglamento regulará composición y funcionamiento de la comisión que proponga al Rector el nombramiento o promoción, además de los criterios de selección y promoción.»</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Composición de la comisión; criterios de promoción entre jerarquías; procedimientos de evaluación</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Estímulos Funcionarios</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Art. 71 Estatuto</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>«La Universidad establecerá políticas de estímulos e incentivos tendientes a fomentar el desarrollo y reconocimiento en la carrera de los funcionarios de apoyo por razones de mérito, perfeccionamiento y capacitación.»</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Políticas de estímulos; criterios de mérito; perfeccionamiento; capacitación; reconocimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>General Estudiantes</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>En Proceso</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Art. 77-79 Estatuto</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Art. 78: Derechos (libertad expresión, igualdad, información, elegir/ser elegido, ambiente propicio, uso bienes). Art. 79: Deberes (fortalecer institución, cumplir normas, respetar autoridades).</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Derechos (Art. 78 a-i); deberes (Art. 79 a-g); definición de estudiante (Art. 65); sistema de identificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Uso de Bienes</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Art. 78 f) Estatuto</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>«A hacer uso de los bienes y servicios de la Universidad, de acuerdo con los reglamentos de uso de estas.»</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Condiciones de uso; préstamo/reserva de espacios; equipamiento; responsabilidades por daño/pérdida</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Disciplinarios Estudiantes</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Art. 80 Estatuto</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>«Estará prohibida y sujeta a sanciones toda conducta atentoria a la dignidad, incluido acoso sexual, laboral y discriminación.» Fiscalía Universitaria a cargo.</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Conductas prohibidas; sanciones; procedimiento sumario; derechos de víctimas (aportar antecedentes, ser notificadas, recursos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Convivencia Universitaria</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Art. 81 Estatuto</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>«Un reglamento aprobado por el CS, a propuesta del CU, normará composición, atribuciones, organización y funcionamiento.» Integrantes de 3 estamentos, elegidos democráticamente, paridad de género.</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Composición triestamental; elección democrática; paridad de género; atribuciones; prevención de violencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Administración Financiera</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Art. 86 g), 89 Estatuto</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>Art. 86 g): Procedimientos para enajenar/gravar activos. Art. 89: Gestión financiera sujeta a reglamentos aprobados por órganos colegiados.</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Enajenación/gravamen de activos; empréstitos; fondos específicos; servicios remunerados; sociedades/fundaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Propiedad Intelectual</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Art. 90 Estatuto</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>«La Universidad establecerá una política de PI que permita fomentar investigación, creación e innovación, resguardando derechos institucionales. Establecerá formas de acceso público al conocimiento.»</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Política PI e industrial; fomento investigación; resguardo derechos; acceso público al conocimiento; respeto derechos de terceros</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Protección de Datos</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Ley 19.628 + Ley 21.094</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Obligación derivada de Ley 19.628 sobre protección de datos personales y normativa de transparencia para universidades del Estado.</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Tratamiento datos personales; medidas de seguridad; derechos ARCO; responsable de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Orden, Higiene y Seguridad</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>En Revisión</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Art. 78 e) Estatuto + DS 594/1999</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Art. 78 e): Derecho a «desempeñar actividades en condiciones de seguridad, salubridad, dignidad.» DS 594: Condiciones sanitarias y ambientales.</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Prevención de riesgos; higiene; seguridad laboral; protocolos de emergencia; condiciones sanitarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Mediador Universitario</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>Art. 81 (derivado)</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Derivado del Art. 81 sobre convivencia. Instancia previa de resolución de conflictos.</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Perfil del mediador; procedimiento de mediación; plazos; efectos del acuerdo; relación con Fiscalía (Art. 39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Emisión de Normas</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Art. 89, 21 Estatuto</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Art. 89: Gestión sujeta a políticas/reglamentos de órganos colegiados. Art. 21: Rector dicta reglamentos, decretos y resoluciones conforme Estatutos.</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Cuándo emitir política vs reglamento vs instructivo vs circular; elementos mínimos; jerarquía normativa interna</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Convenios y Contratos</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Art. 82-86 Estatuto + Ley 19.886</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Art. 83: Contratos sujetos a Ley 19.886. Art. 84: Excepciones para convenios académicos. Art. 85: Licitación privada/trato directo.</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Tramitación de convenios; excepciones Ley 19.886; licitación privada; trato directo; aprobaciones requeridas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Compatibilidad Estudios</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>LEY 21.790 (19/01/2026)</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Art. 2: Dictar normas internas para embarazo, maternidad, paternidad, cuidado de niños y personas con discapacidad. Art. 9: Medidas mínimas obligatorias. Art. 11: Incumplimiento = infracción grave.</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Prioridad inscripción; interrupción sin reprobación; menor % asistencia; 2h alimentación; reprogramación evaluaciones; calendarios especiales; suspensión hasta 2 semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Incentivo al Retiro</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Art. 71 (derivado) + DFL 29/2004</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Derivado de Art. 71 sobre estímulos e incentivos. Marco: Estatuto Administrativo.</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Condiciones de acceso; montos/beneficios; procedimiento; requisitos de antigüedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Votaciones Bienestar</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Art. 78 d) Estatuto + Ley 21.094 Art. 6</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Art. 78 d): Derecho a elegir y ser elegido. Ley 21.094 Art. 6: Participación estamental.</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Procedimiento electoral para bienestar; periodo de votación; representación; coherencia con #6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>⚠ PLAZO GENERAL — Art. Transitorio 1°: «Las restantes medidas y acciones para dictar los reglamentos reseñados en este Estatuto deberán concluirse dentro del plazo máximo de 12 meses contados desde la plena constitución del Consejo Superior.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>Art. Transitorio 4°: «El CU, una vez constituido, iniciará de inmediato un proceso de revisión de normativas y reglamentos internos, para adecuarlas al presente Estatuto.»</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1666,7 +2721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3057,7 +4112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
